--- a/CRM-Session-Work-Log-June-2026.xlsx
+++ b/CRM-Session-Work-Log-June-2026.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="71">
   <si>
     <t>#</t>
   </si>
@@ -226,6 +226,12 @@
   </si>
   <si>
     <t>27.75 hrs</t>
+  </si>
+  <si>
+    <t>PRICE</t>
+  </si>
+  <si>
+    <t>962.5 + 100(Last time) = 1062.5 AUD</t>
   </si>
 </sst>
 </file>
@@ -603,14 +609,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="36.25" customWidth="1"/>
     <col min="4" max="4" width="27.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -624,7 +630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -638,7 +644,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -652,7 +658,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -666,7 +672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -680,7 +686,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -694,7 +700,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -708,7 +714,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -722,7 +728,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -736,7 +742,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -750,7 +756,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -764,7 +770,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -778,7 +784,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -792,7 +798,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -806,7 +812,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -820,7 +826,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -834,7 +840,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -848,7 +854,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -862,7 +868,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -876,7 +882,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -890,7 +896,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -904,7 +910,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -918,7 +924,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -932,7 +938,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -946,7 +952,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -960,7 +966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -974,7 +980,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -988,7 +994,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1002,7 +1008,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1016,8 +1022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1031,7 +1036,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1045,7 +1050,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -1053,16 +1058,16 @@
         <v>66</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:D1 A4:D17 A2:C2 A3:C3 A24:D26 A23:C23 A20:D22 A19:C19 A18:C18 A28:D29 A27:C27 A33:D33 A32:C32 A31:D31" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:D1 A4:D17 A2:C2 A3:C3 A24:D26 A23:C23 A20:D22 A19:C19 A18:C18 A28:D29 A27:C27 A33:B33 A32:C32 A31:D31" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>